--- a/Result/profitability/2436.xlsx
+++ b/Result/profitability/2436.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.17</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.83875</v>
       </c>
       <c r="N2" t="n">
-        <v>29.17</v>
+        <v>29.32125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.22</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5775</v>
+        <v>0.80625</v>
       </c>
       <c r="N3" t="n">
-        <v>27.92125</v>
+        <v>28.02375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.4</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5675</v>
+        <v>0.83875</v>
       </c>
       <c r="N4" t="n">
-        <v>26.91625</v>
+        <v>26.80375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.39</v>
       </c>
       <c r="M5" t="n">
-        <v>0.50125</v>
+        <v>0.7712500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>25.63</v>
+        <v>25.96625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.49</v>
+        <v>0.6375000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>25.08125</v>
+        <v>25.44875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0.36375</v>
+        <v>0.45</v>
       </c>
       <c r="N7" t="n">
-        <v>24.53875</v>
+        <v>24.59</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.28</v>
       </c>
       <c r="M8" t="n">
-        <v>0.19625</v>
+        <v>0.3975000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>23.40875</v>
+        <v>23.1225</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9358,13 +9358,13 @@
         <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L71" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="M71" t="n">
-        <v>0.30375</v>
+        <v>0.3025</v>
       </c>
       <c r="N71" t="n">
         <v>29.59</v>
@@ -9394,10 +9394,10 @@
         <v>114.2</v>
       </c>
       <c r="W71" t="n">
-        <v>0.01999999999999999</v>
+        <v>0.009999999999999981</v>
       </c>
       <c r="X71" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="Y71" t="n">
         <v>-3.59</v>
@@ -9406,10 +9406,10 @@
         <v>-0.1116640746500778</v>
       </c>
       <c r="AA71" t="n">
-        <v>-0.35</v>
+        <v>-0.36</v>
       </c>
       <c r="AB71" t="n">
-        <v>-0.6862745098039216</v>
+        <v>-0.7058823529411764</v>
       </c>
       <c r="AC71" t="n">
         <v>-1.620000000000001</v>
@@ -9485,10 +9485,10 @@
         <v>235</v>
       </c>
       <c r="K72" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L72" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="M72" t="n">
         <v>0.3875</v>
@@ -9521,10 +9521,10 @@
         <v>114.3</v>
       </c>
       <c r="W72" t="n">
-        <v>0.9699999999999999</v>
+        <v>0.9899999999999999</v>
       </c>
       <c r="X72" t="n">
-        <v>6.062499999999999</v>
+        <v>6.6</v>
       </c>
       <c r="Y72" t="n">
         <v>-0.25</v>
@@ -9533,10 +9533,10 @@
         <v>-0.008753501400560193</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AB72" t="n">
-        <v>13.125</v>
+        <v>13.25</v>
       </c>
       <c r="AC72" t="n">
         <v>-1.73</v>
@@ -9648,10 +9648,10 @@
         <v>114.4</v>
       </c>
       <c r="W73" t="n">
-        <v>0.4900000000000002</v>
+        <v>0.4800000000000002</v>
       </c>
       <c r="X73" t="n">
-        <v>0.433628318584071</v>
+        <v>0.4210526315789476</v>
       </c>
       <c r="Y73" t="n">
         <v>2.530000000000001</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2436</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1160</v>
+      </c>
+      <c r="D75" t="n">
+        <v>797</v>
+      </c>
+      <c r="E75" t="n">
+        <v>362</v>
+      </c>
+      <c r="F75" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="G75" t="n">
+        <v>116</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.04%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>409</v>
+      </c>
+      <c r="J75" t="n">
+        <v>525</v>
+      </c>
+      <c r="K75" t="n">
+        <v>459</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.8275</v>
+      </c>
+      <c r="N75" t="n">
+        <v>30.64</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.289999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.06827668455575431</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.690000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.09418767507002812</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
